--- a/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Cidala.xlsx
+++ b/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Cidala.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12525" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="11805" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="redidol" sheetId="1" r:id="rId1"/>
@@ -512,6 +512,9 @@
     <t>上次见到这本书的时候，我刚从卡普尔港出来，也许是掉在附近了。</t>
   </si>
   <si>
+    <t>SpawnZonebeach_cidala()</t>
+  </si>
+  <si>
     <t>なるほど、ポート・カプールの近くか。じゃあ、そっちを探してみるよ。</t>
   </si>
   <si>
@@ -521,9 +524,6 @@
     <t>原来如此，卡普尔港附近，那我就去那边看看吧。</t>
   </si>
   <si>
-    <t>SpawnZonebeach_cidala()</t>
-  </si>
-  <si>
     <t>Cidala_mission_check</t>
   </si>
   <si>
@@ -773,6 +773,9 @@
     <t>团长！就算我们喜欢你，我们也不是你的欲望发泄工具！</t>
   </si>
   <si>
+    <t>mod_affinity(-10)</t>
+  </si>
+  <si>
     <t>これ以上そんな自制のないことをしたら、本気で怒るよ。</t>
   </si>
   <si>
@@ -780,9 +783,6 @@
   </si>
   <si>
     <t>你再这样不节制的话，我们就要生气了。</t>
-  </si>
-  <si>
-    <t>mod_affinity(-10)</t>
   </si>
   <si>
     <t>portrait_set(Cidala_Love)</t>
@@ -1901,7 +1901,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="25" style="2" customWidth="1"/>
@@ -1957,7 +1957,7 @@
     </row>
     <row r="2" spans="9:9">
       <c r="I2" s="2">
-        <f>MAX(I5:I1048520)</f>
+        <f>MAX(I5:I1048522)</f>
         <v>84</v>
       </c>
     </row>
@@ -2905,363 +2905,357 @@
         <v>160</v>
       </c>
     </row>
-    <row r="95" ht="17.25" spans="7:12">
-      <c r="G95" s="2" t="s">
+    <row r="95" ht="17.25" spans="5:11">
+      <c r="E95" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J95" s="10"/>
+      <c r="K95" s="10"/>
+    </row>
+    <row r="96" ht="17.25" spans="7:12">
+      <c r="G96" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I95" s="2">
+      <c r="I96" s="2">
         <v>45</v>
       </c>
-      <c r="J95" s="10" t="s">
+      <c r="J96" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="K96" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5">
+      <c r="E97" s="5"/>
+    </row>
+    <row r="99" ht="17.25" spans="2:12">
+      <c r="B99" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I99" s="2">
+        <v>47</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K99" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1"/>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
+      <c r="B102" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="103" spans="5:6">
+      <c r="E103" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K95" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="96" spans="5:6">
-      <c r="E96" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="98" ht="17.25" spans="2:12">
-      <c r="B98" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I98" s="2">
-        <v>47</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1"/>
-    <row r="100" spans="1:1">
-      <c r="A100" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7">
-      <c r="B101" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="5:6">
-      <c r="E102" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="103" spans="5:7">
-      <c r="E103" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F103" s="2" t="s">
+    </row>
+    <row r="104" spans="5:7">
+      <c r="E104" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" ht="17.25" spans="7:12">
       <c r="G104" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I104" s="2">
-        <v>48</v>
-      </c>
-      <c r="J104" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="K104" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="105" ht="17.25" spans="7:12">
       <c r="G105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I105" s="2">
+        <v>48</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" ht="17.25" spans="7:12">
+      <c r="G106" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I105" s="2">
+      <c r="I106" s="2">
         <v>49</v>
       </c>
-      <c r="J105" s="10" t="s">
+      <c r="J106" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="K105" s="10" t="s">
+      <c r="K106" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="L105" s="2" t="s">
+      <c r="L106" s="2" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="106" spans="5:7">
-      <c r="E106" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F106" s="2" t="s">
+    <row r="107" spans="5:7">
+      <c r="E107" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="107" ht="17.25" spans="7:12">
       <c r="G107" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I107" s="2">
+    </row>
+    <row r="108" ht="17.25" spans="7:12">
+      <c r="G108" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I108" s="2">
         <v>50</v>
       </c>
-      <c r="J107" s="10" t="s">
+      <c r="J108" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="K107" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="L107" s="2" t="s">
+      <c r="L108" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="109" s="2" customFormat="1" ht="17.25" spans="2:12">
-      <c r="B109" s="6" t="s">
+    <row r="110" s="2" customFormat="1" ht="17.25" spans="2:12">
+      <c r="B110" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E110" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I109" s="2">
-        <v>51</v>
-      </c>
-      <c r="J109" s="10" t="s">
+      <c r="I110" s="2">
+        <v>51</v>
+      </c>
+      <c r="J110" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K109" s="10" t="s">
+      <c r="K110" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="L109" s="2" t="s">
+      <c r="L110" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1"/>
-    <row r="111" spans="1:1">
-      <c r="A111" s="4" t="s">
+    <row r="111" s="1" customFormat="1"/>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="112" ht="17.25" spans="7:12">
-      <c r="G112" s="2" t="s">
+    <row r="113" ht="17.25" spans="7:12">
+      <c r="G113" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I112" s="2">
+      <c r="I113" s="2">
         <v>52</v>
       </c>
-      <c r="J112" s="10" t="s">
+      <c r="J113" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K112" s="10" t="s">
+      <c r="K113" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="L112" s="2" t="s">
+      <c r="L113" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="113" spans="5:7">
-      <c r="E113" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F113" s="2" t="s">
+    <row r="114" spans="5:7">
+      <c r="E114" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="114" ht="17.25" spans="5:12">
-      <c r="E114" s="5"/>
       <c r="G114" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I114" s="2">
+    </row>
+    <row r="115" ht="17.25" spans="5:12">
+      <c r="E115" s="5"/>
+      <c r="G115" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I115" s="2">
         <v>53</v>
       </c>
-      <c r="J114" s="10" t="s">
+      <c r="J115" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="K114" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="L114" s="2" t="s">
+      <c r="L115" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="115" spans="5:7">
-      <c r="E115" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F115" s="2" t="s">
+    <row r="116" spans="5:7">
+      <c r="E116" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G115" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="116" ht="17.25" spans="7:12">
       <c r="G116" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I116" s="2">
-        <v>54</v>
-      </c>
-      <c r="J116" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K116" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="117" ht="17.25" spans="7:12">
       <c r="G117" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I117" s="2">
+        <v>54</v>
+      </c>
+      <c r="J117" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="K117" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="118" ht="17.25" spans="7:12">
+      <c r="G118" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I117" s="2">
+      <c r="I118" s="2">
         <v>55</v>
       </c>
-      <c r="J117" s="10" t="s">
+      <c r="J118" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="K117" s="10" t="s">
+      <c r="K118" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="L117" s="2" t="s">
+      <c r="L118" s="2" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="119" ht="17.25" spans="2:12">
-      <c r="B119" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I119" s="2">
-        <v>56</v>
-      </c>
-      <c r="J119" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="K119" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="120" ht="17.25" spans="2:12">
       <c r="B120" s="4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J120" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="K120" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="121" ht="17.25" spans="2:12">
-      <c r="B121" s="6" t="s">
-        <v>30</v>
+      <c r="B121" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I121" s="2">
+        <v>57</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="K121" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="122" ht="17.25" spans="2:12">
+      <c r="B122" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I122" s="2">
         <v>58</v>
       </c>
-      <c r="J121" s="10" t="s">
+      <c r="J122" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="K121" s="10" t="s">
+      <c r="K122" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="L121" s="2" t="s">
+      <c r="L122" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1"/>
-    <row r="123" spans="1:1">
-      <c r="A123" s="4" t="s">
+    <row r="123" s="1" customFormat="1"/>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="124" spans="5:7">
-      <c r="E124" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="125" spans="5:7">
       <c r="E125" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="126" s="2" customFormat="1" spans="5:7">
+    <row r="126" spans="5:7">
       <c r="E126" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>116</v>
@@ -3271,19 +3265,19 @@
       <c r="E127" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="F127" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="128" s="2" customFormat="1" spans="5:7">
+      <c r="E128" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="128" s="2" customFormat="1" spans="5:7">
-      <c r="E128" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>118</v>
@@ -3294,7 +3288,7 @@
         <v>51</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>118</v>
@@ -3305,7 +3299,7 @@
         <v>51</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>118</v>
@@ -3316,55 +3310,49 @@
         <v>51</v>
       </c>
       <c r="F131" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="132" s="2" customFormat="1" spans="5:7">
+      <c r="E132" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="132" spans="5:7">
-      <c r="E132" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="G132" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="133" spans="5:7">
+      <c r="E133" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G132" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="133" spans="7:12">
       <c r="G133" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I133" s="2">
-        <v>59</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="134" spans="7:12">
       <c r="G134" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I134" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="135" spans="7:12">
@@ -3372,106 +3360,106 @@
         <v>116</v>
       </c>
       <c r="I135" s="2">
+        <v>60</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="136" spans="7:12">
+      <c r="G136" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I136" s="2">
         <v>61</v>
       </c>
-      <c r="J135" s="2" t="s">
+      <c r="J136" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="K135" s="2" t="s">
+      <c r="K136" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="L135" s="2" t="s">
+      <c r="L136" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="136" spans="5:7">
-      <c r="E136" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F136" s="2" t="s">
+    <row r="137" spans="5:7">
+      <c r="E137" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G136" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="137" spans="7:12">
       <c r="G137" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I137" s="2">
-        <v>62</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="L137" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="138" spans="7:12">
       <c r="G138" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I138" s="2">
+        <v>62</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="139" spans="7:12">
+      <c r="G139" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I138" s="2">
+      <c r="I139" s="2">
         <v>63</v>
       </c>
-      <c r="J138" s="2" t="s">
+      <c r="J139" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K138" s="2" t="s">
+      <c r="K139" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L138" s="2" t="s">
+      <c r="L139" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="139" spans="5:7">
-      <c r="E139" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F139" s="2" t="s">
+    <row r="140" spans="5:7">
+      <c r="E140" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G139" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="140" spans="7:12">
       <c r="G140" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I140" s="2">
-        <v>64</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="L140" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="141" spans="7:12">
       <c r="G141" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I141" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="142" spans="7:12">
@@ -3479,114 +3467,112 @@
         <v>116</v>
       </c>
       <c r="I142" s="2">
+        <v>65</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="143" spans="7:12">
+      <c r="G143" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I143" s="2">
         <v>66</v>
       </c>
-      <c r="J142" s="2" t="s">
+      <c r="J143" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="K142" s="2" t="s">
+      <c r="K143" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="L142" s="2" t="s">
+      <c r="L143" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="144" spans="2:12">
-      <c r="B144" s="6" t="s">
+    <row r="145" spans="2:12">
+      <c r="B145" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E144" s="5" t="s">
+      <c r="E145" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I144" s="2">
+      <c r="I145" s="2">
         <v>68</v>
       </c>
-      <c r="J144" s="2" t="s">
+      <c r="J145" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="K144" s="2" t="s">
+      <c r="K145" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="L144" s="2" t="s">
+      <c r="L145" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="1"/>
-    <row r="146" spans="1:1">
-      <c r="A146" s="4" t="s">
+    <row r="146" s="1" customFormat="1"/>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="4" t="s">
+    <row r="148" spans="2:6">
+      <c r="B148" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E147" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F147" s="2" t="s">
+      <c r="E148" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="148" spans="5:7">
-      <c r="E148" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F148" s="2" t="s">
+    <row r="149" spans="5:7">
+      <c r="E149" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="149" spans="2:12">
-      <c r="B149" s="6"/>
-      <c r="E149" s="5"/>
       <c r="G149" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I149" s="2">
+    </row>
+    <row r="150" spans="2:12">
+      <c r="B150" s="6"/>
+      <c r="E150" s="5"/>
+      <c r="G150" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I150" s="2">
         <v>71</v>
       </c>
-      <c r="J149" s="2" t="s">
+      <c r="J150" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="K149" s="2" t="s">
+      <c r="K150" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="L149" s="2" t="s">
+      <c r="L150" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="150" spans="2:7">
-      <c r="B150" s="6"/>
-      <c r="E150" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F150" s="2" t="s">
+    <row r="151" spans="2:7">
+      <c r="B151" s="6"/>
+      <c r="E151" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G150" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="151" spans="2:12">
-      <c r="B151" s="6"/>
-      <c r="E151" s="5"/>
       <c r="G151" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="I151" s="2">
-        <v>72</v>
-      </c>
-      <c r="J151" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K151" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="L151" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="152" spans="2:7">
@@ -3595,110 +3581,111 @@
         <v>51</v>
       </c>
       <c r="F152" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="153" spans="2:12">
+      <c r="B153" s="6"/>
+      <c r="E153" s="5"/>
+      <c r="G153" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I153" s="2">
+        <v>72</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="L153" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="153" spans="2:5">
-      <c r="B153" s="6" t="s">
+    </row>
+    <row r="154" spans="2:5">
+      <c r="B154" s="6"/>
+      <c r="E154" s="5"/>
+    </row>
+    <row r="155" spans="2:5">
+      <c r="B155" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="E155" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="1"/>
-    <row r="155" spans="1:1">
-      <c r="A155" s="4" t="s">
+    <row r="156" s="1" customFormat="1"/>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="156" s="2" customFormat="1" spans="5:6">
-      <c r="E156" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F156" s="2" t="s">
+    <row r="158" s="2" customFormat="1" spans="5:6">
+      <c r="E158" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="157" s="2" customFormat="1" spans="9:12">
-      <c r="I157" s="2">
+    <row r="159" s="2" customFormat="1" spans="9:12">
+      <c r="I159" s="2">
         <v>69</v>
       </c>
-      <c r="J157" s="2" t="s">
+      <c r="J159" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="K157" s="2" t="s">
+      <c r="K159" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="L157" s="2" t="s">
+      <c r="L159" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="158" s="2" customFormat="1" spans="5:6">
-      <c r="E158" s="2" t="s">
+    <row r="160" s="2" customFormat="1" spans="5:6">
+      <c r="E160" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F158" s="2" t="s">
+      <c r="F160" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="160" s="2" customFormat="1" spans="2:12">
-      <c r="B160" s="6" t="s">
+    <row r="162" s="2" customFormat="1" spans="2:12">
+      <c r="B162" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E162" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I160" s="2">
+      <c r="I162" s="2">
         <v>70</v>
       </c>
-      <c r="J160" s="2" t="s">
+      <c r="J162" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="K160" s="2" t="s">
+      <c r="K162" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="L160" s="2" t="s">
+      <c r="L162" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1"/>
-    <row r="162" spans="1:1">
-      <c r="A162" s="4" t="s">
+    <row r="163" s="1" customFormat="1"/>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="163" spans="5:7">
-      <c r="E163" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G163" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="164" spans="5:7">
-      <c r="E164" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F164" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="165" spans="5:7">
       <c r="E165" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F165" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="G165" s="2" t="s">
         <v>116</v>
@@ -3708,30 +3695,30 @@
       <c r="E166" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F166" s="2" t="s">
+      <c r="F166" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="167" spans="5:7">
+      <c r="E167" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="168" spans="5:7">
+      <c r="E168" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="167" spans="5:7">
-      <c r="E167" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="168" spans="5:7">
-      <c r="E168" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="G168" s="2" t="s">
         <v>118</v>
@@ -3742,7 +3729,7 @@
         <v>51</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>118</v>
@@ -3753,7 +3740,7 @@
         <v>51</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>118</v>
@@ -3764,182 +3751,175 @@
         <v>51</v>
       </c>
       <c r="F171" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="172" spans="5:7">
+      <c r="E172" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="173" spans="5:7">
+      <c r="E173" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="172" spans="5:7">
-      <c r="E172" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="G173" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="174" spans="5:7">
+      <c r="E174" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="G172" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="173" s="2" customFormat="1" spans="7:12">
-      <c r="G173" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I173" s="2">
+      <c r="G174" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="175" s="2" customFormat="1" spans="7:12">
+      <c r="G175" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I175" s="2">
         <v>73</v>
       </c>
-      <c r="J173" s="2" t="s">
+      <c r="J175" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="K173" s="2" t="s">
+      <c r="K175" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="L173" s="2" t="s">
+      <c r="L175" s="2" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="174" spans="7:12">
-      <c r="G174" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I174" s="2">
-        <v>74</v>
-      </c>
-      <c r="J174" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K174" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="L174" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="175" spans="5:7">
-      <c r="E175" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="176" spans="7:12">
       <c r="G176" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I176" s="2">
+        <v>74</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="177" spans="5:7">
+      <c r="E177" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="178" spans="7:12">
+      <c r="G178" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I178" s="2">
         <v>75</v>
       </c>
-      <c r="J176" s="2" t="s">
+      <c r="J178" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="K176" s="2" t="s">
+      <c r="K178" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="L176" s="2" t="s">
+      <c r="L178" s="2" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="177" spans="7:12">
-      <c r="G177" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I177" s="2">
-        <v>76</v>
-      </c>
-      <c r="J177" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="K177" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="L177" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="178" spans="5:7">
-      <c r="E178" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G178" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="179" spans="7:12">
       <c r="G179" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I179" s="2">
+        <v>76</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="180" spans="5:7">
+      <c r="E180" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="181" spans="7:12">
+      <c r="G181" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I181" s="2">
         <v>77</v>
       </c>
-      <c r="J179" s="2" t="s">
+      <c r="J181" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="K179" s="2" t="s">
+      <c r="K181" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="L179" s="2" t="s">
+      <c r="L181" s="2" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="180" spans="7:12">
-      <c r="G180" s="2" t="s">
+    <row r="182" spans="7:12">
+      <c r="G182" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I180" s="2">
+      <c r="I182" s="2">
         <v>78</v>
       </c>
-      <c r="J180" s="2" t="s">
+      <c r="J182" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K180" s="2" t="s">
+      <c r="K182" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="L180" s="2" t="s">
+      <c r="L182" s="2" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="181" spans="5:6">
-      <c r="E181" s="2" t="s">
+    <row r="183" spans="5:6">
+      <c r="E183" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F181" s="2" t="s">
+      <c r="F183" s="2" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="182" spans="5:7">
-      <c r="E182" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="183" spans="5:12">
-      <c r="E183" s="5"/>
-      <c r="G183" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I183" s="2">
-        <v>80</v>
-      </c>
-      <c r="J183" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K183" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="L183" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="184" spans="5:7">
@@ -3947,98 +3927,127 @@
         <v>51</v>
       </c>
       <c r="F184" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="185" spans="5:12">
+      <c r="E185" s="5"/>
+      <c r="G185" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I185" s="2">
+        <v>80</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="186" spans="5:7">
+      <c r="E186" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G184" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="185" spans="7:12">
-      <c r="G185" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I185" s="2">
-        <v>81</v>
-      </c>
-      <c r="J185" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K185" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="L185" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="186" spans="7:12">
       <c r="G186" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I186" s="2">
-        <v>82</v>
-      </c>
-      <c r="J186" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="K186" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="L186" s="2" t="s">
-        <v>295</v>
+        <v>118</v>
       </c>
     </row>
     <row r="187" spans="7:12">
       <c r="G187" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I187" s="2">
+        <v>81</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="188" spans="7:12">
+      <c r="G188" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I187" s="2">
+      <c r="I188" s="2">
+        <v>82</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="189" spans="7:12">
+      <c r="G189" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I189" s="2">
         <v>83</v>
       </c>
-      <c r="J187" s="2" t="s">
+      <c r="J189" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="K187" s="2" t="s">
+      <c r="K189" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="L187" s="2" t="s">
+      <c r="L189" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="189" spans="2:12">
-      <c r="B189" s="6" t="s">
+    <row r="191" spans="2:12">
+      <c r="B191" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E189" s="5" t="s">
+      <c r="E191" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I189" s="2">
+      <c r="I191" s="2">
         <v>84</v>
       </c>
-      <c r="J189" s="2" t="s">
+      <c r="J191" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="K189" s="2" t="s">
+      <c r="K191" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="L189" s="2" t="s">
+      <c r="L191" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="190" s="1" customFormat="1"/>
-    <row r="191" spans="1:1">
-      <c r="A191" s="4" t="s">
+    <row r="192" s="1" customFormat="1"/>
+    <row r="193" spans="1:1">
+      <c r="A193" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="192" spans="2:5">
-      <c r="B192" s="6" t="s">
+    <row r="194" spans="2:5">
+      <c r="B194" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E192" s="5" t="s">
+      <c r="E194" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="1"/>
+    <row r="195" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Cidala.xlsx
+++ b/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Cidala.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11805" tabRatio="500"/>
+    <workbookView windowWidth="27945" windowHeight="12525" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="redidol" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="309">
   <si>
     <t>step</t>
   </si>
@@ -323,6 +323,12 @@
     <t>约会，然后生蛋！（需要500好感度）</t>
   </si>
   <si>
+    <t>Cidala_world</t>
+  </si>
+  <si>
+    <t>*重现过去的世界*</t>
+  </si>
+  <si>
     <t>最近何か面白いことがあったみたいですね。</t>
   </si>
   <si>
@@ -659,6 +665,9 @@
     <t>mod_flag(cm1end1,=1)</t>
   </si>
   <si>
+    <t>mod_flag(cidalaworld1,=1)</t>
+  </si>
+  <si>
     <t>mod_affinity(200)</t>
   </si>
   <si>
@@ -812,6 +821,9 @@
     <t>那可真是令人兴奋。</t>
   </si>
   <si>
+    <t>mod_flag(cm1end2,=1)</t>
+  </si>
+  <si>
     <t>mod_element(finger,1)</t>
   </si>
   <si>
@@ -924,6 +936,24 @@
   </si>
   <si>
     <t>辛妲拉属性得到了强化</t>
+  </si>
+  <si>
+    <t>你要回忆哪个地方呢？团长。</t>
+  </si>
+  <si>
+    <t>Cidala_world1</t>
+  </si>
+  <si>
+    <t>&gt;=,cidalaworld1,1</t>
+  </si>
+  <si>
+    <t>同人志所在之地</t>
+  </si>
+  <si>
+    <t>回忆已经绽放到了卡普尔港附近。</t>
+  </si>
+  <si>
+    <t>去看看吧。</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +1931,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="25" style="2" customWidth="1"/>
@@ -1957,8 +1987,8 @@
     </row>
     <row r="2" spans="9:9">
       <c r="I2" s="2">
-        <f>MAX(I5:I1048522)</f>
-        <v>84</v>
+        <f>MAX(I5:I1048529)</f>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="5:5">
@@ -2462,847 +2492,857 @@
         <v>97</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" spans="5:5">
+    <row r="56" s="2" customFormat="1" spans="2:12">
+      <c r="B56" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="8"/>
       <c r="E56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I56" s="2">
+        <v>85</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="5:5">
+      <c r="E57" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" spans="2:5">
-      <c r="B57" s="6" t="s">
+    <row r="58" s="2" customFormat="1" spans="2:5">
+      <c r="B58" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1"/>
-    <row r="59" spans="1:1">
-      <c r="A59" s="4" t="s">
+    <row r="59" s="1" customFormat="1"/>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="60" ht="17.25" spans="9:12">
-      <c r="I60" s="2">
+    <row r="61" ht="17.25" spans="9:12">
+      <c r="I61" s="2">
         <v>29</v>
       </c>
-      <c r="J60" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K60" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="L60" s="2" t="s">
+      <c r="J61" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="62" ht="17.25" spans="2:12">
-      <c r="B62" s="4" t="s">
+      <c r="K61" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="L61" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="2">
-        <v>30</v>
-      </c>
-      <c r="J62" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="K62" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="63" ht="17.25" spans="2:12">
       <c r="B63" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I63" s="2">
+        <v>30</v>
+      </c>
+      <c r="J63" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" spans="2:12">
+      <c r="B64" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="2">
         <v>40</v>
       </c>
-      <c r="J63" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K63" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="L63" s="2" t="s">
+      <c r="J64" s="10" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="64" spans="5:5">
-      <c r="E64" s="5" t="s">
+      <c r="K64" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="5:5">
+      <c r="E65" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="2:5">
-      <c r="B65" s="6" t="s">
+    <row r="66" spans="2:5">
+      <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1"/>
-    <row r="67" s="2" customFormat="1" spans="1:1">
-      <c r="A67" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:6">
-      <c r="A68" s="11"/>
-      <c r="E68" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F68" s="2" t="s">
+    <row r="67" s="1" customFormat="1"/>
+    <row r="68" s="2" customFormat="1" spans="1:1">
+      <c r="A68" s="4" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" spans="1:6">
       <c r="A69" s="11"/>
       <c r="E69" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:6">
+      <c r="A70" s="11"/>
+      <c r="E70" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F70" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" spans="1:1">
-      <c r="A70" s="11"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:5">
+    <row r="71" s="2" customFormat="1" spans="1:1">
       <c r="A71" s="11"/>
-      <c r="B71" s="6" t="s">
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:5">
+      <c r="A72" s="11"/>
+      <c r="B72" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E72" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1"/>
-    <row r="73" spans="1:1">
-      <c r="A73" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="74" spans="5:7">
-      <c r="E74" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>116</v>
+    <row r="73" s="1" customFormat="1"/>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="75" spans="5:7">
       <c r="E75" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="F75" s="8" t="s">
         <v>117</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="76" ht="17.25" spans="7:12">
+    <row r="76" spans="5:7">
+      <c r="E76" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="G76" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I76" s="2">
-        <v>32</v>
-      </c>
-      <c r="J76" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K76" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="L76" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77" ht="17.25" spans="7:12">
       <c r="G77" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I77" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J77" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="K77" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="K77" s="10" t="s">
+      <c r="L77" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="78" spans="5:7">
-      <c r="E78" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>125</v>
-      </c>
+    </row>
+    <row r="78" ht="17.25" spans="7:12">
       <c r="G78" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="79" ht="17.25" spans="5:12">
-      <c r="E79" s="5"/>
+      <c r="I78" s="2">
+        <v>33</v>
+      </c>
+      <c r="J78" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79" spans="5:7">
+      <c r="E79" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="G79" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I79" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" ht="17.25" spans="5:12">
+      <c r="E80" s="5"/>
+      <c r="G80" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I80" s="2">
         <v>34</v>
       </c>
-      <c r="J79" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="K79" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="L79" s="2" t="s">
+      <c r="J80" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="80" spans="5:7">
-      <c r="E80" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="K80" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" ht="17.25" spans="5:12">
-      <c r="E81" s="5"/>
+      <c r="L80" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="5:7">
+      <c r="E81" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="G81" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I81" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82" ht="17.25" spans="5:12">
+      <c r="E82" s="5"/>
+      <c r="G82" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I82" s="2">
         <v>35</v>
       </c>
-      <c r="J81" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="L81" s="2" t="s">
+      <c r="J82" s="10" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="82" spans="5:7">
-      <c r="E82" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="K82" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" ht="17.25" spans="7:12">
+      <c r="L82" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="83" spans="5:7">
+      <c r="E83" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="G83" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I83" s="2">
-        <v>36</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="K83" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" ht="17.25" spans="7:12">
       <c r="G84" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I84" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J84" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="K84" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="K84" s="10" t="s">
+      <c r="L84" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="85" spans="5:7">
-      <c r="E85" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>140</v>
-      </c>
+    </row>
+    <row r="85" ht="17.25" spans="7:12">
       <c r="G85" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="86" ht="17.25" spans="7:12">
+      <c r="I85" s="2">
+        <v>37</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="86" spans="5:7">
+      <c r="E86" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G86" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I86" s="2">
-        <v>38</v>
-      </c>
-      <c r="J86" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="K86" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" ht="17.25" spans="7:12">
       <c r="G87" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I87" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J87" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="K87" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K87" s="10" t="s">
+      <c r="L87" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L87" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="88" spans="5:7">
-      <c r="E88" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>147</v>
-      </c>
+    </row>
+    <row r="88" ht="17.25" spans="7:12">
       <c r="G88" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="89" ht="17.25" spans="7:12">
+      <c r="I88" s="2">
+        <v>39</v>
+      </c>
+      <c r="J88" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="K88" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="89" spans="5:7">
+      <c r="E89" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="G89" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I89" s="2">
-        <v>41</v>
-      </c>
-      <c r="J89" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="K89" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" ht="17.25" spans="7:12">
       <c r="G90" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I90" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J90" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K90" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="K90" s="10" t="s">
+      <c r="L90" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L90" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="91" spans="5:7">
-      <c r="E91" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>133</v>
-      </c>
+    </row>
+    <row r="91" ht="17.25" spans="7:12">
       <c r="G91" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="92" ht="17.25" spans="5:12">
-      <c r="E92" s="5"/>
+      <c r="I91" s="2">
+        <v>42</v>
+      </c>
+      <c r="J91" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="K91" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="92" spans="5:7">
+      <c r="E92" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="G92" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="93" ht="17.25" spans="5:12">
+      <c r="E93" s="5"/>
+      <c r="G93" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I93" s="2">
+        <v>43</v>
+      </c>
+      <c r="J93" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="K93" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="94" spans="5:7">
+      <c r="E94" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="95" ht="17.25" spans="7:12">
+      <c r="G95" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I95" s="2">
+        <v>44</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="K95" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="96" ht="17.25" spans="5:11">
+      <c r="E96" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J96" s="10"/>
+      <c r="K96" s="10"/>
+    </row>
+    <row r="97" ht="17.25" spans="7:12">
+      <c r="G97" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I92" s="2">
-        <v>43</v>
-      </c>
-      <c r="J92" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="K92" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="L92" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="93" spans="5:7">
-      <c r="E93" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G93" s="2" t="s">
+      <c r="I97" s="2">
+        <v>45</v>
+      </c>
+      <c r="J97" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="K97" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="5:5">
+      <c r="E98" s="5"/>
+    </row>
+    <row r="100" ht="17.25" spans="2:12">
+      <c r="B100" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" s="2">
+        <v>47</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K100" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1"/>
+    <row r="102" spans="1:1">
+      <c r="A102" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="94" ht="17.25" spans="7:12">
-      <c r="G94" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I94" s="2">
-        <v>44</v>
-      </c>
-      <c r="J94" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="K94" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="L94" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="95" ht="17.25" spans="5:11">
-      <c r="E95" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J95" s="10"/>
-      <c r="K95" s="10"/>
-    </row>
-    <row r="96" ht="17.25" spans="7:12">
-      <c r="G96" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I96" s="2">
-        <v>45</v>
-      </c>
-      <c r="J96" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="K96" s="10" t="s">
+    <row r="104" spans="5:6">
+      <c r="E104" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L96" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="97" spans="5:5">
-      <c r="E97" s="5"/>
-    </row>
-    <row r="99" ht="17.25" spans="2:12">
-      <c r="B99" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I99" s="2">
-        <v>47</v>
-      </c>
-      <c r="J99" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1"/>
-    <row r="101" spans="1:1">
-      <c r="A101" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="102" spans="2:7">
-      <c r="B102" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="103" spans="5:6">
-      <c r="E103" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="104" spans="5:7">
-      <c r="E104" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G104" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" ht="17.25" spans="7:12">
+    </row>
+    <row r="105" spans="5:7">
+      <c r="E105" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="G105" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I105" s="2">
-        <v>48</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="K105" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
     </row>
     <row r="106" ht="17.25" spans="7:12">
       <c r="G106" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I106" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J106" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="K106" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="K106" s="10" t="s">
+      <c r="L106" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="L106" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="107" spans="5:7">
-      <c r="E107" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>133</v>
-      </c>
+    </row>
+    <row r="107" ht="17.25" spans="7:12">
       <c r="G107" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="108" ht="17.25" spans="7:12">
+      <c r="I107" s="2">
+        <v>49</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="5:7">
+      <c r="E108" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="G108" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I108" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="109" ht="17.25" spans="7:12">
+      <c r="G109" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I109" s="2">
         <v>50</v>
       </c>
-      <c r="J108" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="L108" s="2" t="s">
+      <c r="J109" s="10" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="110" s="2" customFormat="1" ht="17.25" spans="2:12">
-      <c r="B110" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E110" s="5" t="s">
+      <c r="K109" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="111" s="2" customFormat="1" ht="17.25" spans="2:12">
+      <c r="B111" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E111" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I110" s="2">
-        <v>51</v>
-      </c>
-      <c r="J110" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="K110" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="L110" s="2" t="s">
+      <c r="I111" s="2">
+        <v>51</v>
+      </c>
+      <c r="J111" s="10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="111" s="1" customFormat="1"/>
-    <row r="112" spans="1:1">
-      <c r="A112" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="113" ht="17.25" spans="7:12">
-      <c r="G113" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I113" s="2">
-        <v>52</v>
-      </c>
-      <c r="J113" s="10" t="s">
+      <c r="K111" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="K113" s="10" t="s">
+      <c r="L111" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="114" spans="5:7">
-      <c r="E114" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>147</v>
-      </c>
+    </row>
+    <row r="112" s="1" customFormat="1"/>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" ht="17.25" spans="7:12">
       <c r="G114" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="115" ht="17.25" spans="5:12">
-      <c r="E115" s="5"/>
+      <c r="I114" s="2">
+        <v>52</v>
+      </c>
+      <c r="J114" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K114" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="115" spans="5:7">
+      <c r="E115" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="G115" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I115" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="116" ht="17.25" spans="5:12">
+      <c r="E116" s="5"/>
+      <c r="G116" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I116" s="2">
         <v>53</v>
       </c>
-      <c r="J115" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="K115" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="L115" s="2" t="s">
+      <c r="J116" s="10" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="116" spans="5:7">
-      <c r="E116" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="117" ht="17.25" spans="7:12">
+      <c r="K116" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="117" spans="5:7">
+      <c r="E117" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G117" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I117" s="2">
-        <v>54</v>
-      </c>
-      <c r="J117" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="K117" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>191</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" ht="17.25" spans="7:12">
       <c r="G118" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I118" s="2">
+        <v>54</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="K118" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="119" ht="17.25" spans="7:12">
+      <c r="G119" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I119" s="2">
         <v>55</v>
       </c>
-      <c r="J118" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="K118" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="L118" s="2" t="s">
+      <c r="J119" s="10" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="120" ht="17.25" spans="2:12">
-      <c r="B120" s="4" t="s">
+      <c r="K119" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E120" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I120" s="2">
-        <v>56</v>
-      </c>
-      <c r="J120" s="10" t="s">
+      <c r="L119" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="K120" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="121" ht="17.25" spans="2:12">
       <c r="B121" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I121" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J121" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="K121" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="L121" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K121" s="10" t="s">
+    </row>
+    <row r="122" ht="17.25" spans="2:12">
+      <c r="B122" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="L121" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="122" ht="17.25" spans="2:12">
-      <c r="B122" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="2">
+        <v>57</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="K122" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="123" ht="17.25" spans="2:12">
+      <c r="B123" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I123" s="2">
         <v>58</v>
       </c>
-      <c r="J122" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="K122" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="L122" s="2" t="s">
+      <c r="J123" s="10" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="123" s="1" customFormat="1"/>
-    <row r="124" spans="1:1">
-      <c r="A124" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="125" spans="5:7">
-      <c r="E125" s="5" t="s">
+      <c r="K123" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F125" s="2" t="s">
+      <c r="L123" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="G125" s="2" t="s">
-        <v>116</v>
+    </row>
+    <row r="124" s="1" customFormat="1"/>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="126" spans="5:7">
       <c r="E126" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F126" s="8" t="s">
         <v>208</v>
       </c>
+      <c r="F126" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="G126" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="127" s="2" customFormat="1" spans="5:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="127" spans="5:7">
       <c r="E127" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" s="2" customFormat="1" spans="5:7">
       <c r="E128" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F128" s="2" t="s">
-        <v>210</v>
+      <c r="F128" s="8" t="s">
+        <v>211</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="129" s="2" customFormat="1" spans="5:7">
-      <c r="E129" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>211</v>
+      <c r="E129" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="130" s="2" customFormat="1" spans="5:7">
-      <c r="E130" s="2" t="s">
+      <c r="E130" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" s="2" customFormat="1" spans="5:7">
@@ -3310,10 +3350,10 @@
         <v>51</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="132" s="2" customFormat="1" spans="5:7">
@@ -3321,83 +3361,77 @@
         <v>51</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="133" spans="5:7">
-      <c r="E133" s="5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="133" s="2" customFormat="1" spans="5:7">
+      <c r="E133" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>140</v>
+        <v>216</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="134" spans="7:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="134" s="2" customFormat="1" spans="5:7">
+      <c r="E134" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>217</v>
+      </c>
       <c r="G134" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I134" s="2">
-        <v>59</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="L134" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="135" spans="7:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="135" spans="5:7">
+      <c r="E135" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G135" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I135" s="2">
-        <v>60</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="L135" s="2" t="s">
-        <v>220</v>
+        <v>120</v>
       </c>
     </row>
     <row r="136" spans="7:12">
       <c r="G136" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I136" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="137" spans="5:7">
-      <c r="E137" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>125</v>
-      </c>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="137" spans="7:12">
       <c r="G137" s="2" t="s">
         <v>118</v>
+      </c>
+      <c r="I137" s="2">
+        <v>60</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="138" spans="7:12">
@@ -3405,7 +3439,7 @@
         <v>118</v>
       </c>
       <c r="I138" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>224</v>
@@ -3417,32 +3451,32 @@
         <v>226</v>
       </c>
     </row>
-    <row r="139" spans="7:12">
+    <row r="139" spans="5:7">
+      <c r="E139" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="G139" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I139" s="2">
-        <v>63</v>
-      </c>
-      <c r="J139" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140" spans="7:12">
+      <c r="G140" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I140" s="2">
+        <v>62</v>
+      </c>
+      <c r="J140" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="K139" s="2" t="s">
+      <c r="K140" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L139" s="2" t="s">
+      <c r="L140" s="2" t="s">
         <v>229</v>
-      </c>
-    </row>
-    <row r="140" spans="5:7">
-      <c r="E140" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="141" spans="7:12">
@@ -3450,7 +3484,7 @@
         <v>118</v>
       </c>
       <c r="I141" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>230</v>
@@ -3462,49 +3496,57 @@
         <v>232</v>
       </c>
     </row>
-    <row r="142" spans="7:12">
+    <row r="142" spans="5:7">
+      <c r="E142" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G142" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I142" s="2">
-        <v>65</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>235</v>
+        <v>120</v>
       </c>
     </row>
     <row r="143" spans="7:12">
       <c r="G143" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I143" s="2">
+        <v>64</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="144" spans="7:12">
+      <c r="G144" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I144" s="2">
+        <v>65</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="145" spans="7:12">
+      <c r="G145" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I145" s="2">
         <v>66</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="L143" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="145" spans="2:12">
-      <c r="B145" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I145" s="2">
-        <v>68</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>239</v>
@@ -3516,208 +3558,206 @@
         <v>241</v>
       </c>
     </row>
-    <row r="146" s="1" customFormat="1"/>
-    <row r="147" spans="1:1">
-      <c r="A147" s="4" t="s">
+    <row r="147" spans="2:12">
+      <c r="B147" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" s="2">
+        <v>68</v>
+      </c>
+      <c r="J147" s="2" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="4" t="s">
+      <c r="K147" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="148" s="1" customFormat="1"/>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E148" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="149" spans="5:7">
-      <c r="E149" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G149" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="150" spans="2:12">
-      <c r="B150" s="6"/>
-      <c r="E150" s="5"/>
-      <c r="G150" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I150" s="2">
+      <c r="E150" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="151" spans="5:7">
+      <c r="E151" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="152" spans="2:12">
+      <c r="B152" s="6"/>
+      <c r="E152" s="5"/>
+      <c r="G152" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I152" s="2">
         <v>71</v>
       </c>
-      <c r="J150" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L150" s="2" t="s">
+      <c r="J152" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="153" spans="2:7">
+      <c r="B153" s="6"/>
+      <c r="E153" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="151" spans="2:7">
-      <c r="B151" s="6"/>
-      <c r="E151" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="152" spans="2:7">
-      <c r="B152" s="6"/>
-      <c r="E152" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="153" spans="2:12">
-      <c r="B153" s="6"/>
-      <c r="E153" s="5"/>
       <c r="G153" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I153" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
+      <c r="B154" s="6"/>
+      <c r="E154" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="155" spans="2:12">
+      <c r="B155" s="6"/>
+      <c r="E155" s="5"/>
+      <c r="G155" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I155" s="2">
         <v>72</v>
       </c>
-      <c r="J153" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="L153" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="154" spans="2:5">
-      <c r="B154" s="6"/>
-      <c r="E154" s="5"/>
-    </row>
-    <row r="155" spans="2:5">
-      <c r="B155" s="6" t="s">
+      <c r="J155" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5">
+      <c r="B156" s="6"/>
+      <c r="E156" s="5"/>
+    </row>
+    <row r="157" spans="2:5">
+      <c r="B157" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E155" s="5" t="s">
+      <c r="E157" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1"/>
-    <row r="157" spans="1:1">
-      <c r="A157" s="4" t="s">
+    <row r="158" s="1" customFormat="1"/>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="158" s="2" customFormat="1" spans="5:6">
-      <c r="E158" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="159" s="2" customFormat="1" spans="9:12">
-      <c r="I159" s="2">
+    <row r="160" s="2" customFormat="1" spans="5:6">
+      <c r="E160" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="161" s="2" customFormat="1" spans="9:12">
+      <c r="I161" s="2">
         <v>69</v>
       </c>
-      <c r="J159" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="K159" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="L159" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="160" s="2" customFormat="1" spans="5:6">
-      <c r="E160" s="2" t="s">
+      <c r="J161" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F160" s="2" t="s">
+      <c r="K161" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="162" s="2" customFormat="1" spans="2:12">
-      <c r="B162" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E162" s="5" t="s">
+      <c r="L161" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="162" s="2" customFormat="1" spans="5:6">
+      <c r="E162" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="164" s="2" customFormat="1" spans="2:12">
+      <c r="B164" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E164" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I162" s="2">
+      <c r="I164" s="2">
         <v>70</v>
       </c>
-      <c r="J162" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="K162" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="L162" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="163" s="1" customFormat="1"/>
-    <row r="164" spans="1:1">
-      <c r="A164" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="165" spans="5:7">
-      <c r="E165" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="166" spans="5:7">
-      <c r="E166" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F166" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>116</v>
+      <c r="J164" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="165" s="1" customFormat="1"/>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="167" spans="5:7">
       <c r="E167" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F167" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>209</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="5:7">
       <c r="E168" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F168" s="2" t="s">
+      <c r="F168" s="8" t="s">
         <v>210</v>
       </c>
       <c r="G168" s="2" t="s">
@@ -3725,36 +3765,36 @@
       </c>
     </row>
     <row r="169" spans="5:7">
-      <c r="E169" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>261</v>
+      <c r="E169" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="170" spans="5:7">
-      <c r="E170" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>262</v>
+    <row r="170" s="2" customFormat="1" spans="5:7">
+      <c r="E170" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>212</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="171" spans="5:7">
-      <c r="E171" s="2" t="s">
+      <c r="E171" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="5:7">
@@ -3762,10 +3802,10 @@
         <v>51</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173" spans="5:7">
@@ -3773,55 +3813,43 @@
         <v>51</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="174" spans="5:7">
-      <c r="E174" s="5" t="s">
+      <c r="E174" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="175" s="2" customFormat="1" spans="7:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="175" spans="5:7">
+      <c r="E175" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="G175" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I175" s="2">
-        <v>73</v>
-      </c>
-      <c r="J175" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K175" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L175" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176" spans="5:7">
+      <c r="E176" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="176" spans="7:12">
       <c r="G176" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I176" s="2">
-        <v>74</v>
-      </c>
-      <c r="J176" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K176" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="L176" s="2" t="s">
-        <v>272</v>
+        <v>120</v>
       </c>
     </row>
     <row r="177" spans="5:7">
@@ -3829,44 +3857,44 @@
         <v>51</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="178" spans="7:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="178" s="2" customFormat="1" spans="7:12">
       <c r="G178" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I178" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J178" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="L178" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="K178" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="L178" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="179" spans="7:12">
       <c r="G179" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I179" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J179" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L179" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="K179" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="L179" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="180" spans="5:7">
@@ -3874,72 +3902,80 @@
         <v>51</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="181" spans="7:12">
       <c r="G181" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I181" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J181" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182" spans="7:12">
       <c r="G182" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I182" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J182" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="183" spans="5:7">
+      <c r="E183" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="K182" s="2" t="s">
+      <c r="G183" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="184" spans="7:12">
+      <c r="G184" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I184" s="2">
+        <v>77</v>
+      </c>
+      <c r="J184" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="L182" s="2" t="s">
+      <c r="K184" s="2" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="183" spans="5:6">
-      <c r="E183" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F183" s="2" t="s">
+      <c r="L184" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="184" spans="5:7">
-      <c r="E184" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="185" spans="5:12">
-      <c r="E185" s="5"/>
+    <row r="185" spans="7:12">
       <c r="G185" s="2" t="s">
         <v>118</v>
       </c>
       <c r="I185" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>287</v>
@@ -3951,103 +3987,256 @@
         <v>289</v>
       </c>
     </row>
-    <row r="186" spans="5:7">
-      <c r="E186" s="5" t="s">
-        <v>51</v>
+    <row r="186" spans="5:6">
+      <c r="E186" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G186" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="187" spans="5:7">
+      <c r="E187" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="188" spans="5:12">
+      <c r="E188" s="5"/>
+      <c r="G188" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I188" s="2">
+        <v>80</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="189" spans="5:7">
+      <c r="E189" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="190" spans="7:12">
+      <c r="G190" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I190" s="2">
+        <v>81</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="191" spans="7:12">
+      <c r="G191" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="187" spans="7:12">
-      <c r="G187" s="2" t="s">
+      <c r="I191" s="2">
+        <v>82</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="192" spans="7:12">
+      <c r="G192" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I187" s="2">
-        <v>81</v>
-      </c>
-      <c r="J187" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="K187" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="L187" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="188" spans="7:12">
-      <c r="G188" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I188" s="2">
-        <v>82</v>
-      </c>
-      <c r="J188" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="K188" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="L188" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="189" spans="7:12">
-      <c r="G189" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I189" s="2">
+      <c r="I192" s="2">
         <v>83</v>
       </c>
-      <c r="J189" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="K189" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="L189" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="191" spans="2:12">
-      <c r="B191" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E191" s="5" t="s">
+      <c r="J192" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="194" spans="2:12">
+      <c r="B194" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E194" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I191" s="2">
+      <c r="I194" s="2">
         <v>84</v>
       </c>
-      <c r="J191" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K191" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L191" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="192" s="1" customFormat="1"/>
-    <row r="193" spans="1:1">
-      <c r="A193" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="194" spans="2:5">
-      <c r="B194" s="6" t="s">
+      <c r="J194" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="195" s="1" customFormat="1"/>
+    <row r="196" spans="1:1">
+      <c r="A196" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5">
+      <c r="B197" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E194" s="5" t="s">
+      <c r="E197" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="195" s="1" customFormat="1"/>
+    <row r="198" s="1" customFormat="1"/>
+    <row r="199" spans="1:1">
+      <c r="A199" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="200" s="2" customFormat="1" spans="5:7">
+      <c r="E200" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="201" s="2" customFormat="1" spans="9:12">
+      <c r="I201" s="2">
+        <v>86</v>
+      </c>
+      <c r="J201" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="K201" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="L201" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="203" s="2" customFormat="1" spans="2:12">
+      <c r="B203" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I203" s="2">
+        <v>87</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5">
+      <c r="B205" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="206" s="1" customFormat="1"/>
+    <row r="207" spans="1:1">
+      <c r="A207" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="208" spans="5:6">
+      <c r="E208" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="209" spans="2:12">
+      <c r="B209" s="6"/>
+      <c r="E209" s="5"/>
+      <c r="I209" s="2">
+        <v>88</v>
+      </c>
+      <c r="J209" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="L209" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5">
+      <c r="B210" s="6"/>
+      <c r="E210" s="5"/>
+    </row>
+    <row r="211" spans="2:12">
+      <c r="B211" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I211" s="2">
+        <v>89</v>
+      </c>
+      <c r="J211" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="L211" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="212" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
